--- a/src/main/resources/files/quote-01.xlsx
+++ b/src/main/resources/files/quote-01.xlsx
@@ -144,47 +144,47 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
+    <t>{{productSpecification}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{customAmount}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{customTax}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{productCustomAmount}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{productCustomUnitPrice}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{productUnit}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{productQuantity}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{productItemName}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{productNo}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
     <t>{{index}}</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>{{productNo}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{productItemName}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{productSpecification}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{productUnit}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{productQuantity}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{productCustomUnitPrice}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{productCustomAmount}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{customAmount}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{customTax}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{customerTotalAmount}}</t>
+    <t>{{customTotalAmount}}</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -1297,28 +1297,28 @@
     </row>
     <row r="12" spans="1:8" s="9" customFormat="1" ht="55.15" customHeight="1">
       <c r="A12" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="16" t="s">
+      <c r="E12" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="19" t="s">
         <v>30</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="10" customFormat="1" ht="55.15" customHeight="1">
@@ -1332,7 +1332,7 @@
         <v>8</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="10" customFormat="1" ht="55.15" customHeight="1">
@@ -1346,7 +1346,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="10" customFormat="1" ht="55.15" customHeight="1">

--- a/src/main/resources/files/quote-01.xlsx
+++ b/src/main/resources/files/quote-01.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\design\src\main\resources\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -144,10 +144,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>{{productSpecification}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>{{customAmount}}</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -156,35 +152,39 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>{{productCustomAmount}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{productCustomUnitPrice}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{productUnit}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{productQuantity}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{productItemName}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{productNo}}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>{{index}}</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>{{customTotalAmount}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{itemNo}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{itemSpec}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{quantity}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{itemUnit}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{itemVendorProductCustomPrice}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{itemVendorProductCustomAmount}}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{itemName}}</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -1297,28 +1297,28 @@
     </row>
     <row r="12" spans="1:8" s="9" customFormat="1" ht="55.15" customHeight="1">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>33</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="10" customFormat="1" ht="55.15" customHeight="1">
@@ -1332,7 +1332,7 @@
         <v>8</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="10" customFormat="1" ht="55.15" customHeight="1">
@@ -1346,7 +1346,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="10" customFormat="1" ht="55.15" customHeight="1">
@@ -1360,7 +1360,7 @@
         <v>10</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
